--- a/Code/Jupiter/Connect4/H2h.xlsx
+++ b/Code/Jupiter/Connect4/H2h.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,6 +1366,38 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PPO_401a</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PPO_402</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1508</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1468</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2526666666666667</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.243–0.262</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/H2h.xlsx
+++ b/Code/Jupiter/Connect4/H2h.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,6 +1398,70 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PPO_403</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PPO_402</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E31" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1468</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.7453333333333333</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.736–0.755</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PPO_403</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PPO_404</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1502</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.4988333333333334</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.481–0.517</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/H2h.xlsx
+++ b/Code/Jupiter/Connect4/H2h.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,6 +1462,38 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PPO_405</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PPO_404</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E33" t="n">
+        <v>34</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.9886666666666667</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.985–0.992</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/H2h.xlsx
+++ b/Code/Jupiter/Connect4/H2h.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1494,166 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PPO_406</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PPO_404</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E34" t="n">
+        <v>33</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9888333333333333</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.985–0.993</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PPO_406</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PPO_405</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1501</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5003333333333333</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.482–0.518</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PPO_406</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EXP_1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2959</v>
+      </c>
+      <c r="E36" t="n">
+        <v>40</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.982–0.991</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PPO_406</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PPO_407</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1491</v>
+      </c>
+      <c r="E37" t="n">
+        <v>32</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1477</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.7431666666666666</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.734–0.752</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PPO_406</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PPO_408</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>52</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2946</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.01766666666666667</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.013–0.022</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/H2h.xlsx
+++ b/Code/Jupiter/Connect4/H2h.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,70 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BASE_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BASE_10</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1508</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1476</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2513333333333334</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.242–0.260</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BASE_11a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BASE_10</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="n">
+        <v>43</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2937</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4961666666666666</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.494–0.499</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
